--- a/backend/prisma/data/expense-line-items.xlsx
+++ b/backend/prisma/data/expense-line-items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887F2C60-6587-4C7D-A763-B33469ABC878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E681B589-E3C0-4621-B39D-7C69588EE7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D30BD04-AED0-48C4-A0F0-DC51EF4C24C2}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="504">
   <si>
     <t>Expense Line Item</t>
   </si>
@@ -1100,9 +1100,6 @@
   </si>
   <si>
     <t>Corporate Finance</t>
-  </si>
-  <si>
-    <t>Admin Services</t>
   </si>
   <si>
     <t>External Affairs</t>
@@ -2212,16 +2209,16 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B2" t="s">
         <v>449</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>450</v>
       </c>
-      <c r="C2" t="s">
-        <v>451</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>214</v>
@@ -2239,10 +2236,10 @@
         <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>24</v>
@@ -2285,18 +2282,18 @@
         <v>225</v>
       </c>
       <c r="F3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L3">
         <v>81123102</v>
@@ -2314,7 +2311,7 @@
         <v>259</v>
       </c>
       <c r="R3" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -2342,13 +2339,13 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L4">
         <v>81123102</v>
@@ -2366,7 +2363,7 @@
         <v>259</v>
       </c>
       <c r="R4" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
@@ -2394,13 +2391,13 @@
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L5">
         <v>81123102</v>
@@ -2418,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="R5" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -2438,7 +2435,7 @@
         <v>AS-27-4</v>
       </c>
       <c r="E6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -2448,13 +2445,13 @@
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L6">
         <v>81123102</v>
@@ -2463,10 +2460,10 @@
         <v>52951101</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -2486,7 +2483,7 @@
         <v>AS-27-5</v>
       </c>
       <c r="E7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -2496,13 +2493,13 @@
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L7">
         <v>80123102</v>
@@ -2511,10 +2508,10 @@
         <v>61721101</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
@@ -2534,19 +2531,19 @@
         <v>AS-27-6</v>
       </c>
       <c r="E8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>276</v>
       </c>
       <c r="I8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L8">
         <v>80123102</v>
@@ -2572,19 +2569,19 @@
         <v>AS-27-7</v>
       </c>
       <c r="E9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>277</v>
       </c>
       <c r="I9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L9">
         <v>80123102</v>
@@ -2610,7 +2607,7 @@
         <v>AS-27-8</v>
       </c>
       <c r="E10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -2618,13 +2615,13 @@
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L10">
         <v>80123102</v>
@@ -2636,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="R10" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -2664,13 +2661,13 @@
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L11">
         <v>81123102</v>
@@ -2688,7 +2685,7 @@
         <v>259</v>
       </c>
       <c r="R11" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -2716,13 +2713,13 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L12">
         <v>80123102</v>
@@ -2731,7 +2728,7 @@
         <v>61711101</v>
       </c>
       <c r="R12" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -2759,13 +2756,13 @@
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L13">
         <v>80123102</v>
@@ -2777,7 +2774,7 @@
         <v>249</v>
       </c>
       <c r="R13" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -2805,13 +2802,13 @@
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L14">
         <v>80123102</v>
@@ -2848,13 +2845,13 @@
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L15">
         <v>80123102</v>
@@ -2863,7 +2860,7 @@
         <v>61111201</v>
       </c>
       <c r="R15" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -2891,13 +2888,13 @@
       <c r="G16"/>
       <c r="H16"/>
       <c r="I16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L16">
         <v>81123102</v>
@@ -2906,16 +2903,16 @@
         <v>52119101</v>
       </c>
       <c r="N16" t="s">
+        <v>419</v>
+      </c>
+      <c r="O16" t="s">
         <v>420</v>
-      </c>
-      <c r="O16" t="s">
-        <v>421</v>
       </c>
       <c r="P16" t="s">
         <v>259</v>
       </c>
       <c r="R16" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
@@ -2943,13 +2940,13 @@
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L17">
         <v>81123102</v>
@@ -2967,7 +2964,7 @@
         <v>259</v>
       </c>
       <c r="R17" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
@@ -2995,13 +2992,13 @@
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L18">
         <v>81123102</v>
@@ -3041,13 +3038,13 @@
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L19">
         <v>81123102</v>
@@ -3087,13 +3084,13 @@
       <c r="G20"/>
       <c r="H20"/>
       <c r="I20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L20">
         <v>80123102</v>
@@ -3111,7 +3108,7 @@
         <v>260</v>
       </c>
       <c r="R20" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
@@ -3139,13 +3136,13 @@
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L21">
         <v>81123102</v>
@@ -3182,13 +3179,13 @@
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L22">
         <v>81123102</v>
@@ -3220,13 +3217,13 @@
         <v>278</v>
       </c>
       <c r="I23" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L23">
         <v>80123102</v>
@@ -3260,13 +3257,13 @@
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J24" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K24" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L24">
         <v>80123102</v>
@@ -3275,7 +3272,7 @@
         <v>61071099</v>
       </c>
       <c r="R24" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -3298,18 +3295,18 @@
         <v>298</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L25">
         <v>81123102</v>
@@ -3343,13 +3340,13 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L26">
         <v>81123102</v>
@@ -3381,18 +3378,18 @@
         <v>298</v>
       </c>
       <c r="F27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L27">
         <v>81123102</v>
@@ -3429,13 +3426,13 @@
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L28">
         <v>81123102</v>
@@ -3447,7 +3444,7 @@
         <v>249</v>
       </c>
       <c r="Q28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
@@ -3470,18 +3467,18 @@
         <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J29" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L29">
         <v>80123102</v>
@@ -3515,13 +3512,13 @@
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J30" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K30" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L30">
         <v>80123102</v>
@@ -3530,10 +3527,10 @@
         <v>61061104</v>
       </c>
       <c r="N30" t="s">
+        <v>379</v>
+      </c>
+      <c r="O30" t="s">
         <v>380</v>
-      </c>
-      <c r="O30" t="s">
-        <v>381</v>
       </c>
       <c r="P30" t="s">
         <v>259</v>
@@ -3564,13 +3561,13 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L31">
         <v>81123102</v>
@@ -3588,7 +3585,7 @@
         <v>259</v>
       </c>
       <c r="R31" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
@@ -3616,13 +3613,13 @@
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J32" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K32" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L32">
         <v>81123102</v>
@@ -3631,7 +3628,7 @@
         <v>52081101</v>
       </c>
       <c r="R32" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
@@ -3659,13 +3656,13 @@
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J33" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K33" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L33">
         <v>81123102</v>
@@ -3674,7 +3671,7 @@
         <v>52081101</v>
       </c>
       <c r="R33" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
@@ -3697,16 +3694,16 @@
         <v>262</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I34" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J34" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K34" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L34" s="9">
         <v>80123102</v>
@@ -3740,13 +3737,13 @@
       <c r="G35"/>
       <c r="H35"/>
       <c r="I35" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L35">
         <v>80123102</v>
@@ -3755,16 +3752,16 @@
         <v>61061104</v>
       </c>
       <c r="N35" t="s">
+        <v>381</v>
+      </c>
+      <c r="O35" t="s">
         <v>382</v>
-      </c>
-      <c r="O35" t="s">
-        <v>383</v>
       </c>
       <c r="P35" t="s">
         <v>260</v>
       </c>
       <c r="R35" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
@@ -3787,22 +3784,25 @@
         <v>264</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I36" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L36">
         <v>80134103</v>
       </c>
       <c r="M36">
         <v>61711101</v>
+      </c>
+      <c r="R36" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
@@ -3822,19 +3822,19 @@
         <v>BCA-27-35</v>
       </c>
       <c r="E37" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I37" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L37">
         <v>80134103</v>
@@ -3860,19 +3860,19 @@
         <v>BCA-27-36</v>
       </c>
       <c r="E38" t="s">
+        <v>501</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>503</v>
-      </c>
       <c r="I38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L38">
         <v>81123102</v>
@@ -3898,19 +3898,19 @@
         <v>BCA-27-37</v>
       </c>
       <c r="E39" t="s">
+        <v>501</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="F39" s="5" t="s">
-        <v>503</v>
-      </c>
       <c r="I39" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L39">
         <v>80123102</v>
@@ -3936,22 +3936,22 @@
         <v>BCA-27-38</v>
       </c>
       <c r="E40" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F40" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I40" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L40">
         <v>80111101</v>
@@ -3980,22 +3980,22 @@
         <v>BCA-27-39</v>
       </c>
       <c r="E41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I41" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L41">
         <v>81111101</v>
@@ -4024,22 +4024,22 @@
         <v>BCA-27-40</v>
       </c>
       <c r="E42" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F42" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I42" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L42">
         <v>90111101</v>
@@ -4073,13 +4073,13 @@
         <v>301</v>
       </c>
       <c r="I43" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L43">
         <v>80349101</v>
@@ -4108,16 +4108,16 @@
         <v>306</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I44" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L44">
         <v>80349101</v>
@@ -4149,13 +4149,13 @@
         <v>307</v>
       </c>
       <c r="I45" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L45">
         <v>81349101</v>
@@ -4187,13 +4187,13 @@
         <v>302</v>
       </c>
       <c r="I46" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L46">
         <v>81349101</v>
@@ -4225,13 +4225,13 @@
         <v>304</v>
       </c>
       <c r="I47" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L47">
         <v>80349101</v>
@@ -4263,13 +4263,13 @@
         <v>305</v>
       </c>
       <c r="I48" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L48">
         <v>81222101</v>
@@ -4301,13 +4301,13 @@
         <v>303</v>
       </c>
       <c r="I49" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L49">
         <v>81349101</v>
@@ -4341,10 +4341,10 @@
         <v>351</v>
       </c>
       <c r="J50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K50" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L50">
         <v>90134102</v>
@@ -4382,10 +4382,10 @@
         <v>351</v>
       </c>
       <c r="J51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K51" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L51">
         <v>90134102</v>
@@ -4427,10 +4427,10 @@
         <v>351</v>
       </c>
       <c r="J52" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K52" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L52">
         <v>90111101</v>
@@ -4462,7 +4462,7 @@
         <v>264</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>219</v>
@@ -4471,10 +4471,10 @@
         <v>351</v>
       </c>
       <c r="J53" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K53" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L53">
         <v>81134102</v>
@@ -4503,7 +4503,7 @@
         <v>264</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>221</v>
@@ -4512,10 +4512,10 @@
         <v>351</v>
       </c>
       <c r="J54" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K54" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L54">
         <v>90134102</v>
@@ -4553,10 +4553,10 @@
         <v>351</v>
       </c>
       <c r="J55" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L55">
         <v>80134102</v>
@@ -4597,10 +4597,10 @@
         <v>351</v>
       </c>
       <c r="J56" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K56" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L56">
         <v>81134102</v>
@@ -4641,10 +4641,10 @@
         <v>351</v>
       </c>
       <c r="J57" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K57" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L57">
         <v>90134102</v>
@@ -4685,10 +4685,10 @@
         <v>351</v>
       </c>
       <c r="J58" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K58" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L58">
         <v>80134102</v>
@@ -4729,10 +4729,10 @@
         <v>351</v>
       </c>
       <c r="J59" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K59" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L59">
         <v>81134102</v>
@@ -4773,10 +4773,10 @@
         <v>351</v>
       </c>
       <c r="J60" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K60" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L60">
         <v>90134102</v>
@@ -4817,10 +4817,10 @@
         <v>351</v>
       </c>
       <c r="J61" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K61" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L61">
         <v>90134102</v>
@@ -4861,10 +4861,10 @@
         <v>351</v>
       </c>
       <c r="J62" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K62" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L62">
         <v>80134102</v>
@@ -4902,10 +4902,10 @@
         <v>351</v>
       </c>
       <c r="J63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K63" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L63">
         <v>90111101</v>
@@ -4943,10 +4943,10 @@
         <v>351</v>
       </c>
       <c r="J64" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K64" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L64">
         <v>90111101</v>
@@ -4987,10 +4987,10 @@
         <v>351</v>
       </c>
       <c r="J65" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K65" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L65">
         <v>80111101</v>
@@ -5031,10 +5031,10 @@
         <v>351</v>
       </c>
       <c r="J66" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K66" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L66">
         <v>81111101</v>
@@ -5075,10 +5075,10 @@
         <v>351</v>
       </c>
       <c r="J67" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K67" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L67">
         <v>80111101</v>
@@ -5119,10 +5119,10 @@
         <v>351</v>
       </c>
       <c r="J68" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K68" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L68">
         <v>81111101</v>
@@ -5160,10 +5160,10 @@
         <v>351</v>
       </c>
       <c r="J69" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K69" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L69">
         <v>81111101</v>
@@ -5201,10 +5201,10 @@
         <v>351</v>
       </c>
       <c r="J70" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K70" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L70">
         <v>81111101</v>
@@ -5245,10 +5245,10 @@
         <v>351</v>
       </c>
       <c r="J71" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K71" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L71">
         <v>80111101</v>
@@ -5289,10 +5289,10 @@
         <v>351</v>
       </c>
       <c r="J72" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K72" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L72">
         <v>81111101</v>
@@ -5333,10 +5333,10 @@
         <v>351</v>
       </c>
       <c r="J73" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K73" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L73">
         <v>90111101</v>
@@ -5365,19 +5365,19 @@
         <v>CF-27-25</v>
       </c>
       <c r="E74" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>481</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>482</v>
       </c>
       <c r="I74" t="s">
         <v>351</v>
       </c>
       <c r="J74" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K74" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L74">
         <v>90134102</v>
@@ -5403,19 +5403,19 @@
         <v>CF-27-26</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I75" t="s">
         <v>351</v>
       </c>
       <c r="J75" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K75" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L75">
         <v>90134102</v>
@@ -5444,7 +5444,7 @@
         <v>247</v>
       </c>
       <c r="F76" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G76" t="s">
         <v>219</v>
@@ -5454,10 +5454,10 @@
         <v>351</v>
       </c>
       <c r="J76" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K76" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L76">
         <v>81134102</v>
@@ -5495,10 +5495,10 @@
         <v>351</v>
       </c>
       <c r="J77" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K77" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L77">
         <v>80134102</v>
@@ -5536,10 +5536,10 @@
         <v>351</v>
       </c>
       <c r="J78" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K78" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L78">
         <v>80134102</v>
@@ -5577,10 +5577,10 @@
         <v>351</v>
       </c>
       <c r="J79" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K79" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L79">
         <v>80134102</v>
@@ -5612,16 +5612,16 @@
         <v>313</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I80" t="s">
         <v>351</v>
       </c>
       <c r="J80" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K80" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L80">
         <v>80134102</v>
@@ -5660,10 +5660,10 @@
         <v>165</v>
       </c>
       <c r="J81" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K81" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L81">
         <v>81314101</v>
@@ -5703,10 +5703,10 @@
         <v>165</v>
       </c>
       <c r="J82" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K82" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L82">
         <v>81314101</v>
@@ -5746,10 +5746,10 @@
         <v>165</v>
       </c>
       <c r="J83" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K83" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L83">
         <v>81314101</v>
@@ -5789,10 +5789,10 @@
         <v>165</v>
       </c>
       <c r="J84" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K84" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L84">
         <v>81314101</v>
@@ -5832,10 +5832,10 @@
         <v>165</v>
       </c>
       <c r="J85" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K85" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L85">
         <v>81314101</v>
@@ -5875,10 +5875,10 @@
         <v>165</v>
       </c>
       <c r="J86" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K86" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L86">
         <v>81314101</v>
@@ -5918,10 +5918,10 @@
         <v>165</v>
       </c>
       <c r="J87" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K87" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L87">
         <v>81314101</v>
@@ -5961,10 +5961,10 @@
         <v>165</v>
       </c>
       <c r="J88" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K88" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L88">
         <v>81314101</v>
@@ -6004,10 +6004,10 @@
         <v>165</v>
       </c>
       <c r="J89" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K89" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L89">
         <v>81314101</v>
@@ -6035,22 +6035,22 @@
         <v>EA-27-1</v>
       </c>
       <c r="E90" t="s">
+        <v>353</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I90" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J90" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K90" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L90">
         <v>80125101</v>
@@ -6076,22 +6076,22 @@
         <v>EA-27-2</v>
       </c>
       <c r="E91" t="s">
+        <v>353</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I91" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J91" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K91" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L91">
         <v>81125101</v>
@@ -6117,22 +6117,22 @@
         <v>EA-27-3</v>
       </c>
       <c r="E92" t="s">
+        <v>353</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I92" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J92" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K92" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L92">
         <v>90125101</v>
@@ -6158,19 +6158,19 @@
         <v>EA-27-4</v>
       </c>
       <c r="E93" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I93" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J93" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K93" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L93">
         <v>80125101</v>
@@ -6199,19 +6199,19 @@
         <v>289</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I94" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J94" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K94" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L94">
         <v>80125101</v>
@@ -6240,19 +6240,19 @@
         <v>289</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I95" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J95" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K95" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L95">
         <v>81125101</v>
@@ -6281,19 +6281,19 @@
         <v>289</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I96" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J96" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K96" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L96">
         <v>90125101</v>
@@ -6329,10 +6329,10 @@
         <v>84</v>
       </c>
       <c r="J97" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K97" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L97">
         <v>81122101</v>
@@ -6372,10 +6372,10 @@
         <v>84</v>
       </c>
       <c r="J98" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K98" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L98">
         <v>81122101</v>
@@ -6415,10 +6415,10 @@
         <v>84</v>
       </c>
       <c r="J99" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K99" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L99">
         <v>81122101</v>
@@ -6458,10 +6458,10 @@
         <v>84</v>
       </c>
       <c r="J100" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K100" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L100">
         <v>81122101</v>
@@ -6501,10 +6501,10 @@
         <v>84</v>
       </c>
       <c r="J101" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K101" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L101">
         <v>81122101</v>
@@ -6544,10 +6544,10 @@
         <v>84</v>
       </c>
       <c r="J102" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K102" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L102">
         <v>81122101</v>
@@ -6587,10 +6587,10 @@
         <v>84</v>
       </c>
       <c r="J103" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K103" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L103">
         <v>81122101</v>
@@ -6630,10 +6630,10 @@
         <v>84</v>
       </c>
       <c r="J104" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K104" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L104">
         <v>81122101</v>
@@ -6665,7 +6665,7 @@
         <v>215</v>
       </c>
       <c r="F105" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G105"/>
       <c r="H105"/>
@@ -6673,10 +6673,10 @@
         <v>84</v>
       </c>
       <c r="J105" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K105" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L105">
         <v>81122101</v>
@@ -6716,10 +6716,10 @@
         <v>84</v>
       </c>
       <c r="J106" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K106" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L106">
         <v>81122101</v>
@@ -6759,10 +6759,10 @@
         <v>84</v>
       </c>
       <c r="J107" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K107" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L107">
         <v>81122101</v>
@@ -6802,10 +6802,10 @@
         <v>84</v>
       </c>
       <c r="J108" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K108" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L108">
         <v>81122101</v>
@@ -6845,10 +6845,10 @@
         <v>84</v>
       </c>
       <c r="J109" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K109" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L109">
         <v>81122101</v>
@@ -6888,10 +6888,10 @@
         <v>84</v>
       </c>
       <c r="J110" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L110">
         <v>81122101</v>
@@ -6931,10 +6931,10 @@
         <v>84</v>
       </c>
       <c r="J111" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K111" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L111">
         <v>81122101</v>
@@ -6974,10 +6974,10 @@
         <v>84</v>
       </c>
       <c r="J112" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K112" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L112">
         <v>81122101</v>
@@ -7017,10 +7017,10 @@
         <v>84</v>
       </c>
       <c r="J113" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K113" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L113">
         <v>81122101</v>
@@ -7060,10 +7060,10 @@
         <v>84</v>
       </c>
       <c r="J114" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K114" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L114">
         <v>81122101</v>
@@ -7103,10 +7103,10 @@
         <v>84</v>
       </c>
       <c r="J115" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K115" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L115">
         <v>81122101</v>
@@ -7146,10 +7146,10 @@
         <v>84</v>
       </c>
       <c r="J116" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K116" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L116">
         <v>90122101</v>
@@ -7189,10 +7189,10 @@
         <v>84</v>
       </c>
       <c r="J117" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K117" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L117">
         <v>90122101</v>
@@ -7232,10 +7232,10 @@
         <v>84</v>
       </c>
       <c r="J118" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L118">
         <v>81122101</v>
@@ -7244,10 +7244,10 @@
         <v>52121402</v>
       </c>
       <c r="N118" t="s">
+        <v>393</v>
+      </c>
+      <c r="O118" t="s">
         <v>394</v>
-      </c>
-      <c r="O118" t="s">
-        <v>395</v>
       </c>
       <c r="P118" t="s">
         <v>259</v>
@@ -7284,10 +7284,10 @@
         <v>84</v>
       </c>
       <c r="J119" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K119" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L119">
         <v>81122101</v>
@@ -7319,7 +7319,7 @@
         <v>268</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -7327,10 +7327,10 @@
         <v>84</v>
       </c>
       <c r="J120" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K120" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L120">
         <v>81122101</v>
@@ -7339,13 +7339,13 @@
         <v>52121402</v>
       </c>
       <c r="N120" t="s">
+        <v>393</v>
+      </c>
+      <c r="O120" t="s">
         <v>394</v>
       </c>
-      <c r="O120" t="s">
-        <v>395</v>
-      </c>
       <c r="P120" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="R120" t="s">
         <v>84</v>
@@ -7379,10 +7379,10 @@
         <v>84</v>
       </c>
       <c r="J121" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L121">
         <v>81122101</v>
@@ -7391,13 +7391,13 @@
         <v>52121402</v>
       </c>
       <c r="N121" t="s">
+        <v>401</v>
+      </c>
+      <c r="O121" t="s">
         <v>402</v>
       </c>
-      <c r="O121" t="s">
-        <v>403</v>
-      </c>
       <c r="P121" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="R121" t="s">
         <v>84</v>
@@ -7433,10 +7433,10 @@
         <v>84</v>
       </c>
       <c r="J122" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K122" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L122">
         <v>90122101</v>
@@ -7445,13 +7445,13 @@
         <v>52121310</v>
       </c>
       <c r="N122" t="s">
+        <v>393</v>
+      </c>
+      <c r="O122" t="s">
         <v>394</v>
       </c>
-      <c r="O122" t="s">
-        <v>395</v>
-      </c>
       <c r="P122" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R122" t="s">
         <v>84</v>
@@ -7487,10 +7487,10 @@
         <v>84</v>
       </c>
       <c r="J123" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K123" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L123">
         <v>81122101</v>
@@ -7499,13 +7499,13 @@
         <v>52121310</v>
       </c>
       <c r="N123" t="s">
+        <v>393</v>
+      </c>
+      <c r="O123" t="s">
         <v>394</v>
       </c>
-      <c r="O123" t="s">
-        <v>395</v>
-      </c>
       <c r="P123" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R123" t="s">
         <v>84</v>
@@ -7541,10 +7541,10 @@
         <v>84</v>
       </c>
       <c r="J124" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K124" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L124">
         <v>80122101</v>
@@ -7553,13 +7553,13 @@
         <v>61021311</v>
       </c>
       <c r="N124" t="s">
+        <v>393</v>
+      </c>
+      <c r="O124" t="s">
         <v>394</v>
       </c>
-      <c r="O124" t="s">
-        <v>395</v>
-      </c>
       <c r="P124" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R124" t="s">
         <v>84</v>
@@ -7585,7 +7585,7 @@
         <v>268</v>
       </c>
       <c r="F125" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G125"/>
       <c r="H125"/>
@@ -7593,10 +7593,10 @@
         <v>84</v>
       </c>
       <c r="J125" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K125" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L125">
         <v>81122101</v>
@@ -7605,10 +7605,10 @@
         <v>52121402</v>
       </c>
       <c r="N125" t="s">
+        <v>397</v>
+      </c>
+      <c r="O125" t="s">
         <v>398</v>
-      </c>
-      <c r="O125" t="s">
-        <v>399</v>
       </c>
       <c r="P125" t="s">
         <v>259</v>
@@ -7637,7 +7637,7 @@
         <v>268</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -7645,10 +7645,10 @@
         <v>84</v>
       </c>
       <c r="J126" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K126" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L126">
         <v>81122101</v>
@@ -7657,10 +7657,10 @@
         <v>52121402</v>
       </c>
       <c r="N126" t="s">
+        <v>386</v>
+      </c>
+      <c r="O126" t="s">
         <v>387</v>
-      </c>
-      <c r="O126" t="s">
-        <v>388</v>
       </c>
       <c r="P126" t="s">
         <v>259</v>
@@ -7697,10 +7697,10 @@
         <v>84</v>
       </c>
       <c r="J127" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L127">
         <v>81122101</v>
@@ -7709,10 +7709,10 @@
         <v>52121315</v>
       </c>
       <c r="N127" t="s">
+        <v>383</v>
+      </c>
+      <c r="O127" t="s">
         <v>384</v>
-      </c>
-      <c r="O127" t="s">
-        <v>385</v>
       </c>
       <c r="P127" t="s">
         <v>259</v>
@@ -7749,10 +7749,10 @@
         <v>84</v>
       </c>
       <c r="J128" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K128" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L128">
         <v>81122101</v>
@@ -7761,10 +7761,10 @@
         <v>52121402</v>
       </c>
       <c r="N128" t="s">
+        <v>393</v>
+      </c>
+      <c r="O128" t="s">
         <v>394</v>
-      </c>
-      <c r="O128" t="s">
-        <v>395</v>
       </c>
       <c r="P128" t="s">
         <v>259</v>
@@ -7801,10 +7801,10 @@
         <v>84</v>
       </c>
       <c r="J129" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L129">
         <v>81122101</v>
@@ -7813,13 +7813,13 @@
         <v>52121402</v>
       </c>
       <c r="N129" t="s">
+        <v>399</v>
+      </c>
+      <c r="O129" t="s">
         <v>400</v>
       </c>
-      <c r="O129" t="s">
-        <v>401</v>
-      </c>
       <c r="P129" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="R129" t="s">
         <v>84</v>
@@ -7853,10 +7853,10 @@
         <v>84</v>
       </c>
       <c r="J130" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K130" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L130">
         <v>81122101</v>
@@ -7899,10 +7899,10 @@
         <v>84</v>
       </c>
       <c r="J131" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K131" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L131">
         <v>81122101</v>
@@ -7942,10 +7942,10 @@
         <v>84</v>
       </c>
       <c r="J132" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K132" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L132">
         <v>81122101</v>
@@ -7985,10 +7985,10 @@
         <v>84</v>
       </c>
       <c r="J133" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K133" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L133">
         <v>81122101</v>
@@ -7997,13 +7997,13 @@
         <v>52121402</v>
       </c>
       <c r="N133" t="s">
+        <v>393</v>
+      </c>
+      <c r="O133" t="s">
         <v>394</v>
       </c>
-      <c r="O133" t="s">
-        <v>395</v>
-      </c>
       <c r="P133" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="R133" t="s">
         <v>84</v>
@@ -8037,10 +8037,10 @@
         <v>84</v>
       </c>
       <c r="J134" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K134" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L134">
         <v>81122101</v>
@@ -8049,13 +8049,13 @@
         <v>52121402</v>
       </c>
       <c r="N134" t="s">
+        <v>395</v>
+      </c>
+      <c r="O134" t="s">
         <v>396</v>
       </c>
-      <c r="O134" t="s">
-        <v>397</v>
-      </c>
       <c r="P134" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="R134" t="s">
         <v>84</v>
@@ -8091,10 +8091,10 @@
         <v>84</v>
       </c>
       <c r="J135" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K135" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L135">
         <v>90111101</v>
@@ -8103,13 +8103,13 @@
         <v>52121314</v>
       </c>
       <c r="N135" t="s">
+        <v>393</v>
+      </c>
+      <c r="O135" t="s">
         <v>394</v>
       </c>
-      <c r="O135" t="s">
-        <v>395</v>
-      </c>
       <c r="P135" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R135" t="s">
         <v>84</v>
@@ -8145,10 +8145,10 @@
         <v>84</v>
       </c>
       <c r="J136" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K136" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L136">
         <v>80111101</v>
@@ -8157,13 +8157,13 @@
         <v>61021315</v>
       </c>
       <c r="N136" t="s">
+        <v>393</v>
+      </c>
+      <c r="O136" t="s">
         <v>394</v>
       </c>
-      <c r="O136" t="s">
-        <v>395</v>
-      </c>
       <c r="P136" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R136" t="s">
         <v>84</v>
@@ -8199,10 +8199,10 @@
         <v>84</v>
       </c>
       <c r="J137" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K137" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L137">
         <v>81111101</v>
@@ -8211,13 +8211,13 @@
         <v>52121314</v>
       </c>
       <c r="N137" t="s">
+        <v>393</v>
+      </c>
+      <c r="O137" t="s">
         <v>394</v>
       </c>
-      <c r="O137" t="s">
-        <v>395</v>
-      </c>
       <c r="P137" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R137" t="s">
         <v>84</v>
@@ -8251,10 +8251,10 @@
         <v>84</v>
       </c>
       <c r="J138" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K138" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L138">
         <v>81122101</v>
@@ -8289,7 +8289,7 @@
         <v>268</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
@@ -8297,10 +8297,10 @@
         <v>84</v>
       </c>
       <c r="J139" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K139" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L139">
         <v>81122101</v>
@@ -8309,13 +8309,13 @@
         <v>52121402</v>
       </c>
       <c r="N139" t="s">
+        <v>388</v>
+      </c>
+      <c r="O139" t="s">
         <v>389</v>
       </c>
-      <c r="O139" t="s">
+      <c r="P139" t="s">
         <v>390</v>
-      </c>
-      <c r="P139" t="s">
-        <v>391</v>
       </c>
       <c r="R139" t="s">
         <v>84</v>
@@ -8349,10 +8349,10 @@
         <v>84</v>
       </c>
       <c r="J140" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K140" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L140">
         <v>90122101</v>
@@ -8384,7 +8384,7 @@
         <v>325</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>221</v>
@@ -8394,10 +8394,10 @@
         <v>84</v>
       </c>
       <c r="J141" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K141" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L141">
         <v>90122101</v>
@@ -8429,7 +8429,7 @@
         <v>325</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>219</v>
@@ -8439,10 +8439,10 @@
         <v>84</v>
       </c>
       <c r="J142" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K142" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L142">
         <v>81122101</v>
@@ -8474,7 +8474,7 @@
         <v>325</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>220</v>
@@ -8484,10 +8484,10 @@
         <v>84</v>
       </c>
       <c r="J143" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K143" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L143">
         <v>80122101</v>
@@ -8524,10 +8524,10 @@
         <v>84</v>
       </c>
       <c r="J144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K144" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L144">
         <v>90111101</v>
@@ -8567,10 +8567,10 @@
         <v>84</v>
       </c>
       <c r="J145" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K145" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L145">
         <v>90122101</v>
@@ -8602,7 +8602,7 @@
         <v>325</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -8610,10 +8610,10 @@
         <v>84</v>
       </c>
       <c r="J146" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K146" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L146">
         <v>90122101</v>
@@ -8653,10 +8653,10 @@
         <v>84</v>
       </c>
       <c r="J147" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K147" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L147">
         <v>90122101</v>
@@ -8694,10 +8694,10 @@
         <v>84</v>
       </c>
       <c r="J148" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K148" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L148">
         <v>90122101</v>
@@ -8739,10 +8739,10 @@
         <v>84</v>
       </c>
       <c r="J149" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K149" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L149">
         <v>80111101</v>
@@ -8784,10 +8784,10 @@
         <v>84</v>
       </c>
       <c r="J150" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K150" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L150">
         <v>90111101</v>
@@ -8829,10 +8829,10 @@
         <v>84</v>
       </c>
       <c r="J151" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K151" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L151">
         <v>81111101</v>
@@ -8872,10 +8872,10 @@
         <v>84</v>
       </c>
       <c r="J152" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K152" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L152">
         <v>81122101</v>
@@ -8915,10 +8915,10 @@
         <v>84</v>
       </c>
       <c r="J153" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K153" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L153">
         <v>81122101</v>
@@ -8958,10 +8958,10 @@
         <v>84</v>
       </c>
       <c r="J154" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K154" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L154">
         <v>81122101</v>
@@ -9001,10 +9001,10 @@
         <v>84</v>
       </c>
       <c r="J155" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K155" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L155">
         <v>81122101</v>
@@ -9044,10 +9044,10 @@
         <v>84</v>
       </c>
       <c r="J156" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K156" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L156">
         <v>81122101</v>
@@ -9079,7 +9079,7 @@
         <v>312</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
@@ -9087,10 +9087,10 @@
         <v>84</v>
       </c>
       <c r="J157" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K157" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L157">
         <v>81122101</v>
@@ -9119,7 +9119,7 @@
         <v>HR-27-15</v>
       </c>
       <c r="E158" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>164</v>
@@ -9132,10 +9132,10 @@
         <v>84</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K158" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L158">
         <v>81122101</v>
@@ -9167,7 +9167,7 @@
         <v>HR-27-16</v>
       </c>
       <c r="E159" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>164</v>
@@ -9180,10 +9180,10 @@
         <v>84</v>
       </c>
       <c r="J159" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K159" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L159">
         <v>90122101</v>
@@ -9228,10 +9228,10 @@
         <v>84</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K160" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L160">
         <v>81111101</v>
@@ -9273,10 +9273,10 @@
         <v>84</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K161" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L161">
         <v>80111101</v>
@@ -9318,10 +9318,10 @@
         <v>84</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K162" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L162">
         <v>90111101</v>
@@ -9363,10 +9363,10 @@
         <v>84</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K163" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L163">
         <v>81111101</v>
@@ -9408,10 +9408,10 @@
         <v>84</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K164" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L164">
         <v>80111101</v>
@@ -9453,10 +9453,10 @@
         <v>84</v>
       </c>
       <c r="J165" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K165" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L165">
         <v>90111101</v>
@@ -9498,10 +9498,10 @@
         <v>84</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K166" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L166">
         <v>81111101</v>
@@ -9543,10 +9543,10 @@
         <v>84</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K167" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L167">
         <v>80111101</v>
@@ -9588,10 +9588,10 @@
         <v>84</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K168" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L168">
         <v>90111101</v>
@@ -9633,10 +9633,10 @@
         <v>84</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K169" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L169">
         <v>90111101</v>
@@ -9678,10 +9678,10 @@
         <v>84</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K170" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L170">
         <v>81111101</v>
@@ -9723,10 +9723,10 @@
         <v>84</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K171" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L171">
         <v>81111101</v>
@@ -9768,10 +9768,10 @@
         <v>84</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K172" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L172">
         <v>80111101</v>
@@ -9813,10 +9813,10 @@
         <v>84</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K173" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L173">
         <v>90111101</v>
@@ -9858,10 +9858,10 @@
         <v>84</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K174" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L174">
         <v>81111101</v>
@@ -9903,10 +9903,10 @@
         <v>84</v>
       </c>
       <c r="J175" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K175" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L175">
         <v>80111101</v>
@@ -9948,10 +9948,10 @@
         <v>84</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K176" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L176">
         <v>90111101</v>
@@ -9993,10 +9993,10 @@
         <v>84</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K177" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L177">
         <v>81111101</v>
@@ -10038,10 +10038,10 @@
         <v>84</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K178" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L178">
         <v>80111101</v>
@@ -10083,10 +10083,10 @@
         <v>84</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K179" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L179">
         <v>90111101</v>
@@ -10128,10 +10128,10 @@
         <v>84</v>
       </c>
       <c r="J180" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K180" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L180">
         <v>80111101</v>
@@ -10173,10 +10173,10 @@
         <v>84</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K181" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L181">
         <v>80111101</v>
@@ -10218,10 +10218,10 @@
         <v>84</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K182" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L182">
         <v>90111101</v>
@@ -10263,10 +10263,10 @@
         <v>84</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K183" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L183">
         <v>81111101</v>
@@ -10308,10 +10308,10 @@
         <v>84</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K184" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L184">
         <v>81111101</v>
@@ -10351,10 +10351,10 @@
         <v>84</v>
       </c>
       <c r="J185" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K185" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L185">
         <v>90111101</v>
@@ -10386,7 +10386,7 @@
         <v>265</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G186" s="4"/>
       <c r="H186" s="4"/>
@@ -10394,10 +10394,10 @@
         <v>84</v>
       </c>
       <c r="J186" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K186" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L186">
         <v>90111101</v>
@@ -10438,10 +10438,10 @@
         <v>84</v>
       </c>
       <c r="J187" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K187" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L187">
         <v>80111101</v>
@@ -10482,10 +10482,10 @@
         <v>84</v>
       </c>
       <c r="J188" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K188" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L188">
         <v>90111101</v>
@@ -10527,10 +10527,10 @@
         <v>84</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K189" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L189">
         <v>90111101</v>
@@ -10572,10 +10572,10 @@
         <v>84</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K190" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L190">
         <v>90111101</v>
@@ -10617,10 +10617,10 @@
         <v>84</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K191" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L191">
         <v>81111101</v>
@@ -10662,10 +10662,10 @@
         <v>84</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K192" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L192">
         <v>80111101</v>
@@ -10707,10 +10707,10 @@
         <v>84</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K193" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L193">
         <v>90111101</v>
@@ -10739,7 +10739,7 @@
         <v>HR-27-51</v>
       </c>
       <c r="E194" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>341</v>
@@ -10748,10 +10748,10 @@
         <v>84</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K194" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L194">
         <v>81111101</v>
@@ -10780,7 +10780,7 @@
         <v>HR-27-52</v>
       </c>
       <c r="E195" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>341</v>
@@ -10789,10 +10789,10 @@
         <v>84</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K195" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L195">
         <v>80111101</v>
@@ -10821,7 +10821,7 @@
         <v>HR-27-53</v>
       </c>
       <c r="E196" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>341</v>
@@ -10830,10 +10830,10 @@
         <v>84</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K196" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L196">
         <v>90111101</v>
@@ -10862,10 +10862,10 @@
         <v>HR-27-54</v>
       </c>
       <c r="E197" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F197" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>219</v>
@@ -10875,10 +10875,10 @@
         <v>84</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K197" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L197">
         <v>81111101</v>
@@ -10907,10 +10907,10 @@
         <v>HR-27-55</v>
       </c>
       <c r="E198" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F198" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G198" s="5" t="s">
         <v>220</v>
@@ -10920,10 +10920,10 @@
         <v>84</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K198" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L198">
         <v>80111101</v>
@@ -10952,10 +10952,10 @@
         <v>HR-27-56</v>
       </c>
       <c r="E199" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F199" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>221</v>
@@ -10965,10 +10965,10 @@
         <v>84</v>
       </c>
       <c r="J199" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K199" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L199">
         <v>90111101</v>
@@ -10997,10 +10997,10 @@
         <v>HR-27-57</v>
       </c>
       <c r="E200" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F200" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>219</v>
@@ -11010,10 +11010,10 @@
         <v>84</v>
       </c>
       <c r="J200" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K200" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L200">
         <v>81111101</v>
@@ -11042,10 +11042,10 @@
         <v>HR-27-58</v>
       </c>
       <c r="E201" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F201" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>220</v>
@@ -11055,10 +11055,10 @@
         <v>84</v>
       </c>
       <c r="J201" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K201" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L201">
         <v>80111101</v>
@@ -11087,10 +11087,10 @@
         <v>HR-27-59</v>
       </c>
       <c r="E202" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F202" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G202" s="5" t="s">
         <v>221</v>
@@ -11100,10 +11100,10 @@
         <v>84</v>
       </c>
       <c r="J202" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K202" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L202">
         <v>90111101</v>
@@ -11132,10 +11132,10 @@
         <v>HR-27-60</v>
       </c>
       <c r="E203" t="s">
+        <v>357</v>
+      </c>
+      <c r="F203" t="s">
         <v>358</v>
-      </c>
-      <c r="F203" t="s">
-        <v>359</v>
       </c>
       <c r="G203" s="5" t="s">
         <v>219</v>
@@ -11145,10 +11145,10 @@
         <v>84</v>
       </c>
       <c r="J203" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K203" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L203">
         <v>81111101</v>
@@ -11177,10 +11177,10 @@
         <v>HR-27-61</v>
       </c>
       <c r="E204" t="s">
+        <v>357</v>
+      </c>
+      <c r="F204" t="s">
         <v>358</v>
-      </c>
-      <c r="F204" t="s">
-        <v>359</v>
       </c>
       <c r="G204" s="5" t="s">
         <v>220</v>
@@ -11190,10 +11190,10 @@
         <v>84</v>
       </c>
       <c r="J204" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K204" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L204">
         <v>80111101</v>
@@ -11222,10 +11222,10 @@
         <v>HR-27-62</v>
       </c>
       <c r="E205" t="s">
+        <v>357</v>
+      </c>
+      <c r="F205" t="s">
         <v>358</v>
-      </c>
-      <c r="F205" t="s">
-        <v>359</v>
       </c>
       <c r="G205" s="5" t="s">
         <v>221</v>
@@ -11235,10 +11235,10 @@
         <v>84</v>
       </c>
       <c r="J205" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K205" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L205">
         <v>90111101</v>
@@ -11267,7 +11267,7 @@
         <v>HR-27-63</v>
       </c>
       <c r="E206" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>342</v>
@@ -11276,10 +11276,10 @@
         <v>84</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K206" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L206">
         <v>81111101</v>
@@ -11308,7 +11308,7 @@
         <v>HR-27-64</v>
       </c>
       <c r="E207" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>342</v>
@@ -11317,10 +11317,10 @@
         <v>84</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K207" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L207">
         <v>80111101</v>
@@ -11349,7 +11349,7 @@
         <v>HR-27-65</v>
       </c>
       <c r="E208" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>342</v>
@@ -11358,10 +11358,10 @@
         <v>84</v>
       </c>
       <c r="J208" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K208" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L208">
         <v>90111101</v>
@@ -11390,7 +11390,7 @@
         <v>HR-27-66</v>
       </c>
       <c r="E209" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>343</v>
@@ -11399,10 +11399,10 @@
         <v>84</v>
       </c>
       <c r="J209" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K209" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L209">
         <v>81111101</v>
@@ -11431,7 +11431,7 @@
         <v>HR-27-67</v>
       </c>
       <c r="E210" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>344</v>
@@ -11443,10 +11443,10 @@
         <v>84</v>
       </c>
       <c r="J210" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K210" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L210">
         <v>80111101</v>
@@ -11475,7 +11475,7 @@
         <v>HR-27-68</v>
       </c>
       <c r="E211" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>344</v>
@@ -11487,10 +11487,10 @@
         <v>84</v>
       </c>
       <c r="J211" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K211" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L211">
         <v>90111101</v>
@@ -11519,7 +11519,7 @@
         <v>HR-27-69</v>
       </c>
       <c r="E212" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>346</v>
@@ -11531,10 +11531,10 @@
         <v>84</v>
       </c>
       <c r="J212" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K212" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L212">
         <v>80111101</v>
@@ -11563,7 +11563,7 @@
         <v>HR-27-70</v>
       </c>
       <c r="E213" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>346</v>
@@ -11575,10 +11575,10 @@
         <v>84</v>
       </c>
       <c r="J213" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K213" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L213">
         <v>90111101</v>
@@ -11610,16 +11610,16 @@
         <v>267</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I214" t="s">
         <v>84</v>
       </c>
       <c r="J214" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K214" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L214">
         <v>81122101</v>
@@ -11656,10 +11656,10 @@
         <v>84</v>
       </c>
       <c r="J215" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K215" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L215">
         <v>81122101</v>
@@ -11696,10 +11696,10 @@
         <v>84</v>
       </c>
       <c r="J216" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K216" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L216">
         <v>81122101</v>
@@ -11736,10 +11736,10 @@
         <v>84</v>
       </c>
       <c r="J217" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K217" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L217">
         <v>81122101</v>
@@ -11768,16 +11768,16 @@
         <v>267</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I218" t="s">
         <v>84</v>
       </c>
       <c r="J218" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K218" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L218">
         <v>81122101</v>
@@ -11814,10 +11814,10 @@
         <v>84</v>
       </c>
       <c r="J219" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K219" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L219">
         <v>81122101</v>
@@ -11854,10 +11854,10 @@
         <v>84</v>
       </c>
       <c r="J220" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K220" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L220">
         <v>81122101</v>
@@ -11894,10 +11894,10 @@
         <v>84</v>
       </c>
       <c r="J221" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K221" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L221">
         <v>81122101</v>
@@ -11932,10 +11932,10 @@
         <v>84</v>
       </c>
       <c r="J222" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K222" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L222">
         <v>81134102</v>
@@ -11972,10 +11972,10 @@
         <v>84</v>
       </c>
       <c r="J223" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K223" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L223">
         <v>81122101</v>
@@ -12004,7 +12004,7 @@
         <v>267</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G224" s="4"/>
       <c r="H224" s="4"/>
@@ -12012,10 +12012,10 @@
         <v>84</v>
       </c>
       <c r="J224" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K224" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L224">
         <v>81122101</v>
@@ -12052,10 +12052,10 @@
         <v>84</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K225" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L225">
         <v>81122101</v>
@@ -12095,10 +12095,10 @@
         <v>84</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K226" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L226">
         <v>81122101</v>
@@ -12138,10 +12138,10 @@
         <v>84</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K227" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L227">
         <v>81122101</v>
@@ -12181,10 +12181,10 @@
         <v>84</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K228" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L228">
         <v>81122101</v>
@@ -12224,10 +12224,10 @@
         <v>84</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K229" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L229">
         <v>81122101</v>
@@ -12267,10 +12267,10 @@
         <v>84</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K230" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L230">
         <v>81122101</v>
@@ -12310,10 +12310,10 @@
         <v>84</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K231" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L231">
         <v>81122101</v>
@@ -12353,10 +12353,10 @@
         <v>84</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K232" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L232">
         <v>81122101</v>
@@ -12365,13 +12365,13 @@
         <v>52121315</v>
       </c>
       <c r="N232" t="s">
+        <v>393</v>
+      </c>
+      <c r="O232" t="s">
         <v>394</v>
       </c>
-      <c r="O232" t="s">
-        <v>395</v>
-      </c>
       <c r="P232" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="R232" t="s">
         <v>84</v>
@@ -12405,10 +12405,10 @@
         <v>84</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K233" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L233">
         <v>81122101</v>
@@ -12448,10 +12448,10 @@
         <v>84</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K234" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L234">
         <v>81122101</v>
@@ -12491,10 +12491,10 @@
         <v>84</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K235" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L235">
         <v>81122101</v>
@@ -12534,10 +12534,10 @@
         <v>84</v>
       </c>
       <c r="J236" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K236" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L236">
         <v>81122101</v>
@@ -12577,10 +12577,10 @@
         <v>84</v>
       </c>
       <c r="J237" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K237" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L237">
         <v>81122101</v>
@@ -12612,7 +12612,7 @@
         <v>131</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G238" s="4"/>
       <c r="H238" s="4"/>
@@ -12620,10 +12620,10 @@
         <v>84</v>
       </c>
       <c r="J238" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K238" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L238">
         <v>81122101</v>
@@ -12663,10 +12663,10 @@
         <v>84</v>
       </c>
       <c r="J239" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K239" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L239">
         <v>81122101</v>
@@ -12706,10 +12706,10 @@
         <v>84</v>
       </c>
       <c r="J240" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K240" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L240">
         <v>81122101</v>
@@ -12749,10 +12749,10 @@
         <v>84</v>
       </c>
       <c r="J241" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K241" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L241">
         <v>81122101</v>
@@ -12780,16 +12780,16 @@
         <v>325</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I242" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J242" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K242" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L242">
         <v>81124101</v>
@@ -12818,16 +12818,16 @@
         <v>325</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I243" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J243" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K243" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L243">
         <v>81124101</v>
@@ -12856,16 +12856,16 @@
         <v>325</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J244" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K244" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L244">
         <v>81124101</v>
@@ -12894,16 +12894,16 @@
         <v>325</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I245" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J245" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K245" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L245">
         <v>81124101</v>
@@ -12932,16 +12932,16 @@
         <v>325</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I246" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J246" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K246" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L246">
         <v>81124101</v>
@@ -12970,16 +12970,16 @@
         <v>325</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I247" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J247" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K247" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L247">
         <v>81124101</v>
@@ -13011,13 +13011,13 @@
         <v>295</v>
       </c>
       <c r="I248" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J248" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K248" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L248">
         <v>80124101</v>
@@ -13052,13 +13052,13 @@
         <v>297</v>
       </c>
       <c r="I249" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J249" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K249" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L249">
         <v>80124101</v>
@@ -13093,13 +13093,13 @@
         <v>292</v>
       </c>
       <c r="I250" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J250" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K250" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L250">
         <v>80124101</v>
@@ -13134,13 +13134,13 @@
         <v>296</v>
       </c>
       <c r="I251" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J251" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K251" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L251">
         <v>80124101</v>
@@ -13175,13 +13175,13 @@
         <v>293</v>
       </c>
       <c r="I252" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J252" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K252" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L252">
         <v>80124101</v>
@@ -13216,13 +13216,13 @@
         <v>294</v>
       </c>
       <c r="I253" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J253" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K253" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L253">
         <v>80124101</v>
@@ -13254,16 +13254,16 @@
         <v>291</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I254" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J254" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K254" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L254">
         <v>80124101</v>
@@ -13301,13 +13301,13 @@
         <v>206</v>
       </c>
       <c r="I255" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J255" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K255" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L255">
         <v>81124101</v>
@@ -13333,7 +13333,7 @@
         <v>IT-27-15</v>
       </c>
       <c r="E256" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>48</v>
@@ -13342,13 +13342,13 @@
         <v>185</v>
       </c>
       <c r="I256" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J256" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K256" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L256">
         <v>81124101</v>
@@ -13377,7 +13377,7 @@
         <v>IT-27-16</v>
       </c>
       <c r="E257" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>47</v>
@@ -13386,13 +13386,13 @@
         <v>201</v>
       </c>
       <c r="I257" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J257" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K257" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L257">
         <v>81124101</v>
@@ -13421,20 +13421,20 @@
         <v>IT-27-17</v>
       </c>
       <c r="E258" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H258"/>
       <c r="I258" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J258" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K258" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L258">
         <v>81124101</v>
@@ -13472,13 +13472,13 @@
         <v>198</v>
       </c>
       <c r="I259" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J259" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K259" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L259">
         <v>80124101</v>
@@ -13516,13 +13516,13 @@
         <v>173</v>
       </c>
       <c r="I260" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J260" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K260" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L260">
         <v>81124101</v>
@@ -13560,13 +13560,13 @@
         <v>190</v>
       </c>
       <c r="I261" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J261" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K261" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L261">
         <v>80124101</v>
@@ -13604,13 +13604,13 @@
         <v>202</v>
       </c>
       <c r="I262" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J262" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K262" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L262">
         <v>80124101</v>
@@ -13648,13 +13648,13 @@
         <v>205</v>
       </c>
       <c r="I263" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J263" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K263" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L263">
         <v>80124101</v>
@@ -13683,22 +13683,22 @@
         <v>IT-27-23</v>
       </c>
       <c r="E264" t="s">
+        <v>416</v>
+      </c>
+      <c r="F264" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I264" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J264" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K264" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L264">
         <v>81124101</v>
@@ -13724,22 +13724,22 @@
         <v>IT-27-24</v>
       </c>
       <c r="E265" t="s">
+        <v>416</v>
+      </c>
+      <c r="F265" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="G265" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I265" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J265" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K265" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L265">
         <v>80124101</v>
@@ -13765,22 +13765,22 @@
         <v>IT-27-25</v>
       </c>
       <c r="E266" t="s">
+        <v>416</v>
+      </c>
+      <c r="F266" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="G266" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I266" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J266" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K266" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L266">
         <v>90124101</v>
@@ -13806,22 +13806,22 @@
         <v>IT-27-26</v>
       </c>
       <c r="E267" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G267" s="5" t="s">
         <v>219</v>
       </c>
       <c r="I267" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J267" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K267" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L267">
         <v>81124101</v>
@@ -13847,22 +13847,22 @@
         <v>IT-27-27</v>
       </c>
       <c r="E268" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G268" s="5" t="s">
         <v>220</v>
       </c>
       <c r="I268" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J268" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K268" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L268">
         <v>80124101</v>
@@ -13888,22 +13888,22 @@
         <v>IT-27-28</v>
       </c>
       <c r="E269" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G269" s="5" t="s">
         <v>221</v>
       </c>
       <c r="I269" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J269" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K269" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L269">
         <v>90124101</v>
@@ -13938,13 +13938,13 @@
         <v>168</v>
       </c>
       <c r="I270" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J270" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K270" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L270">
         <v>81124101</v>
@@ -13976,19 +13976,19 @@
         <v>208</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H271" t="s">
         <v>178</v>
       </c>
       <c r="I271" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J271" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K271" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L271">
         <v>80124101</v>
@@ -14026,13 +14026,13 @@
         <v>182</v>
       </c>
       <c r="I272" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J272" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K272" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L272">
         <v>80124101</v>
@@ -14070,13 +14070,13 @@
         <v>187</v>
       </c>
       <c r="I273" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J273" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K273" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L273">
         <v>80124101</v>
@@ -14114,13 +14114,13 @@
         <v>188</v>
       </c>
       <c r="I274" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J274" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K274" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L274">
         <v>80124101</v>
@@ -14158,13 +14158,13 @@
         <v>189</v>
       </c>
       <c r="I275" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J275" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K275" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L275">
         <v>80124101</v>
@@ -14202,13 +14202,13 @@
         <v>197</v>
       </c>
       <c r="I276" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J276" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K276" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L276">
         <v>80124101</v>
@@ -14240,17 +14240,17 @@
         <v>208</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H277"/>
       <c r="I277" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J277" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K277" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L277">
         <v>80124101</v>
@@ -14288,13 +14288,13 @@
         <v>200</v>
       </c>
       <c r="I278" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J278" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K278" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L278">
         <v>81124101</v>
@@ -14332,13 +14332,13 @@
         <v>204</v>
       </c>
       <c r="I279" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J279" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K279" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L279">
         <v>81124101</v>
@@ -14370,17 +14370,17 @@
         <v>208</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H280"/>
       <c r="I280" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J280" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K280" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L280">
         <v>81124101</v>
@@ -14418,13 +14418,13 @@
         <v>176</v>
       </c>
       <c r="I281" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J281" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K281" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L281">
         <v>80124101</v>
@@ -14462,13 +14462,13 @@
         <v>167</v>
       </c>
       <c r="I282" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J282" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K282" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L282">
         <v>81124101</v>
@@ -14506,13 +14506,13 @@
         <v>169</v>
       </c>
       <c r="I283" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J283" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K283" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L283">
         <v>80124101</v>
@@ -14547,13 +14547,13 @@
         <v>170</v>
       </c>
       <c r="I284" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J284" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K284" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L284">
         <v>80124101</v>
@@ -14588,13 +14588,13 @@
         <v>171</v>
       </c>
       <c r="I285" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J285" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K285" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L285">
         <v>80124101</v>
@@ -14623,17 +14623,17 @@
         <v>211</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H286"/>
       <c r="I286" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J286" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K286" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L286">
         <v>80124101</v>
@@ -14662,17 +14662,17 @@
         <v>211</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H287"/>
       <c r="I287" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J287" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K287" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L287">
         <v>81124101</v>
@@ -14707,13 +14707,13 @@
         <v>174</v>
       </c>
       <c r="I288" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J288" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K288" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L288">
         <v>81124101</v>
@@ -14742,17 +14742,17 @@
         <v>211</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H289"/>
       <c r="I289" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J289" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K289" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L289">
         <v>81124101</v>
@@ -14787,13 +14787,13 @@
         <v>177</v>
       </c>
       <c r="I290" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J290" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K290" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L290">
         <v>80124101</v>
@@ -14826,13 +14826,13 @@
       </c>
       <c r="H291"/>
       <c r="I291" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J291" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K291" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L291">
         <v>81124101</v>
@@ -14867,13 +14867,13 @@
         <v>181</v>
       </c>
       <c r="I292" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J292" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K292" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L292">
         <v>80124101</v>
@@ -14911,13 +14911,13 @@
         <v>183</v>
       </c>
       <c r="I293" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J293" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K293" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L293">
         <v>80124101</v>
@@ -14955,13 +14955,13 @@
         <v>184</v>
       </c>
       <c r="I294" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J294" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K294" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L294">
         <v>81124101</v>
@@ -14996,13 +14996,13 @@
         <v>186</v>
       </c>
       <c r="I295" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J295" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K295" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L295">
         <v>80124101</v>
@@ -15040,13 +15040,13 @@
         <v>191</v>
       </c>
       <c r="I296" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J296" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K296" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L296">
         <v>80124101</v>
@@ -15075,17 +15075,17 @@
         <v>211</v>
       </c>
       <c r="F297" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H297"/>
       <c r="I297" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J297" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K297" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L297">
         <v>81124101</v>
@@ -15114,19 +15114,19 @@
         <v>211</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H298" t="s">
         <v>192</v>
       </c>
       <c r="I298" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J298" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K298" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L298">
         <v>81124101</v>
@@ -15164,13 +15164,13 @@
         <v>193</v>
       </c>
       <c r="I299" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J299" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K299" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L299">
         <v>80124101</v>
@@ -15208,13 +15208,13 @@
         <v>194</v>
       </c>
       <c r="I300" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J300" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K300" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L300">
         <v>80124101</v>
@@ -15252,13 +15252,13 @@
         <v>195</v>
       </c>
       <c r="I301" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J301" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K301" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L301">
         <v>80124101</v>
@@ -15293,13 +15293,13 @@
         <v>196</v>
       </c>
       <c r="I302" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J302" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K302" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L302">
         <v>80124101</v>
@@ -15332,13 +15332,13 @@
       </c>
       <c r="H303"/>
       <c r="I303" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J303" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K303" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L303">
         <v>80124101</v>
@@ -15370,17 +15370,17 @@
         <v>211</v>
       </c>
       <c r="F304" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H304"/>
       <c r="I304" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J304" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K304" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L304">
         <v>81124101</v>
@@ -15415,13 +15415,13 @@
         <v>199</v>
       </c>
       <c r="I305" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J305" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K305" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L305">
         <v>80124101</v>
@@ -15456,13 +15456,13 @@
         <v>203</v>
       </c>
       <c r="I306" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J306" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K306" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L306">
         <v>81124101</v>
@@ -15495,13 +15495,13 @@
       </c>
       <c r="H307"/>
       <c r="I307" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J307" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K307" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L307">
         <v>80124101</v>
@@ -15536,13 +15536,13 @@
         <v>180</v>
       </c>
       <c r="I308" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J308" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K308" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L308">
         <v>81124101</v>
@@ -15574,16 +15574,16 @@
         <v>264</v>
       </c>
       <c r="F309" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I309" s="5" t="s">
         <v>323</v>
       </c>
       <c r="J309" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K309" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L309">
         <v>90122101</v>
@@ -15620,10 +15620,10 @@
         <v>323</v>
       </c>
       <c r="J310" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K310" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L310">
         <v>80123101</v>
@@ -15664,10 +15664,10 @@
         <v>323</v>
       </c>
       <c r="J311" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K311" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L311">
         <v>90123101</v>
@@ -15708,10 +15708,10 @@
         <v>323</v>
       </c>
       <c r="J312" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K312" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L312">
         <v>81123101</v>
@@ -15749,10 +15749,10 @@
         <v>323</v>
       </c>
       <c r="J313" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K313" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L313">
         <v>80123101</v>
@@ -15790,10 +15790,10 @@
         <v>323</v>
       </c>
       <c r="J314" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K314" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L314">
         <v>80123101</v>
@@ -15831,10 +15831,10 @@
         <v>323</v>
       </c>
       <c r="J315" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K315" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L315">
         <v>80123101</v>
@@ -15872,10 +15872,10 @@
         <v>323</v>
       </c>
       <c r="J316" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K316" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L316">
         <v>80123101</v>
@@ -15913,10 +15913,10 @@
         <v>323</v>
       </c>
       <c r="J317" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K317" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L317">
         <v>80123101</v>
@@ -15948,16 +15948,16 @@
         <v>333</v>
       </c>
       <c r="F318" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I318" t="s">
         <v>323</v>
       </c>
       <c r="J318" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K318" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L318">
         <v>80123101</v>
@@ -15998,10 +15998,10 @@
         <v>323</v>
       </c>
       <c r="J319" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K319" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L319">
         <v>80123101</v>
@@ -16039,10 +16039,10 @@
         <v>323</v>
       </c>
       <c r="J320" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K320" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L320">
         <v>81123101</v>
@@ -16077,10 +16077,10 @@
         <v>323</v>
       </c>
       <c r="J321" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K321" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L321">
         <v>80123101</v>
@@ -16118,10 +16118,10 @@
         <v>323</v>
       </c>
       <c r="J322" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K322" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L322">
         <v>90123101</v>
@@ -16159,10 +16159,10 @@
         <v>323</v>
       </c>
       <c r="J323" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K323" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L323">
         <v>90122101</v>
@@ -16202,10 +16202,10 @@
         <v>290</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K324" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L324">
         <v>81111204</v>
@@ -16243,10 +16243,10 @@
         <v>290</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K325" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L325">
         <v>90111204</v>
@@ -16284,10 +16284,10 @@
         <v>290</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K326" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L326">
         <v>80111204</v>
@@ -16322,10 +16322,10 @@
         <v>290</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K327" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="L327">
         <v>81134102</v>
@@ -16334,7 +16334,7 @@
         <v>52952101</v>
       </c>
       <c r="R327" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.35">
@@ -16362,10 +16362,10 @@
         <v>300</v>
       </c>
       <c r="J328" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K328" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L328">
         <v>81319101</v>
@@ -16403,10 +16403,10 @@
         <v>300</v>
       </c>
       <c r="J329" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K329" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L329">
         <v>81319101</v>
@@ -16444,10 +16444,10 @@
         <v>300</v>
       </c>
       <c r="J330" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K330" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L330">
         <v>81319101</v>
@@ -16488,10 +16488,10 @@
         <v>300</v>
       </c>
       <c r="J331" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K331" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L331">
         <v>81319101</v>
@@ -16529,10 +16529,10 @@
         <v>300</v>
       </c>
       <c r="J332" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K332" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L332">
         <v>81319101</v>
@@ -16570,10 +16570,10 @@
         <v>300</v>
       </c>
       <c r="J333" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K333" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L333">
         <v>81319101</v>
@@ -16611,10 +16611,10 @@
         <v>300</v>
       </c>
       <c r="J334" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K334" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L334">
         <v>81319101</v>
@@ -16652,10 +16652,10 @@
         <v>300</v>
       </c>
       <c r="J335" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K335" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L335">
         <v>81319101</v>
@@ -16687,16 +16687,16 @@
         <v>264</v>
       </c>
       <c r="F336" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I336" t="s">
         <v>350</v>
       </c>
       <c r="J336" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K336" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L336">
         <v>80133103</v>
@@ -16734,10 +16734,10 @@
         <v>350</v>
       </c>
       <c r="J337" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K337" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L337">
         <v>81133103</v>
@@ -16778,10 +16778,10 @@
         <v>350</v>
       </c>
       <c r="J338" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K338" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L338">
         <v>80133103</v>
@@ -16822,10 +16822,10 @@
         <v>86</v>
       </c>
       <c r="J339" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K339" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L339">
         <v>80133102</v>
@@ -16867,10 +16867,10 @@
         <v>86</v>
       </c>
       <c r="J340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K340" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L340">
         <v>81133102</v>
@@ -16912,10 +16912,10 @@
         <v>86</v>
       </c>
       <c r="J341" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K341" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L341">
         <v>90133102</v>
@@ -16947,7 +16947,7 @@
         <v>247</v>
       </c>
       <c r="F342" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G342"/>
       <c r="H342"/>
@@ -16955,10 +16955,10 @@
         <v>86</v>
       </c>
       <c r="J342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K342" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L342">
         <v>80133102</v>
@@ -16990,7 +16990,7 @@
         <v>247</v>
       </c>
       <c r="F343" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G343" t="s">
         <v>220</v>
@@ -17000,10 +17000,10 @@
         <v>86</v>
       </c>
       <c r="J343" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K343" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L343">
         <v>80111101</v>
@@ -17035,7 +17035,7 @@
         <v>247</v>
       </c>
       <c r="F344" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G344" t="s">
         <v>219</v>
@@ -17045,10 +17045,10 @@
         <v>86</v>
       </c>
       <c r="J344" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K344" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L344">
         <v>81111101</v>
@@ -17080,7 +17080,7 @@
         <v>247</v>
       </c>
       <c r="F345" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G345" t="s">
         <v>221</v>
@@ -17090,10 +17090,10 @@
         <v>86</v>
       </c>
       <c r="J345" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K345" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L345">
         <v>90111101</v>
@@ -17125,7 +17125,7 @@
         <v>247</v>
       </c>
       <c r="F346" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G346" t="s">
         <v>221</v>
@@ -17135,10 +17135,10 @@
         <v>86</v>
       </c>
       <c r="J346" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K346" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L346">
         <v>90111101</v>
@@ -17170,7 +17170,7 @@
         <v>247</v>
       </c>
       <c r="F347" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G347" t="s">
         <v>220</v>
@@ -17180,10 +17180,10 @@
         <v>86</v>
       </c>
       <c r="J347" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K347" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L347">
         <v>80111101</v>
@@ -17215,7 +17215,7 @@
         <v>247</v>
       </c>
       <c r="F348" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G348" t="s">
         <v>219</v>
@@ -17225,10 +17225,10 @@
         <v>86</v>
       </c>
       <c r="J348" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K348" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L348">
         <v>81111101</v>
@@ -17260,7 +17260,7 @@
         <v>247</v>
       </c>
       <c r="F349" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G349" t="s">
         <v>221</v>
@@ -17270,10 +17270,10 @@
         <v>86</v>
       </c>
       <c r="J349" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L349">
         <v>90111101</v>
@@ -17305,7 +17305,7 @@
         <v>247</v>
       </c>
       <c r="F350" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G350" t="s">
         <v>221</v>
@@ -17315,10 +17315,10 @@
         <v>86</v>
       </c>
       <c r="J350" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K350" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L350">
         <v>90111101</v>
@@ -17350,7 +17350,7 @@
         <v>247</v>
       </c>
       <c r="F351" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G351" t="s">
         <v>219</v>
@@ -17360,10 +17360,10 @@
         <v>86</v>
       </c>
       <c r="J351" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K351" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L351">
         <v>81111101</v>
@@ -17395,7 +17395,7 @@
         <v>247</v>
       </c>
       <c r="F352" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G352" t="s">
         <v>221</v>
@@ -17405,10 +17405,10 @@
         <v>86</v>
       </c>
       <c r="J352" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K352" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L352">
         <v>90111101</v>
@@ -17440,7 +17440,7 @@
         <v>247</v>
       </c>
       <c r="F353" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G353" t="s">
         <v>221</v>
@@ -17450,10 +17450,10 @@
         <v>86</v>
       </c>
       <c r="J353" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K353" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L353">
         <v>90111101</v>
@@ -17485,7 +17485,7 @@
         <v>247</v>
       </c>
       <c r="F354" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G354" t="s">
         <v>220</v>
@@ -17495,10 +17495,10 @@
         <v>86</v>
       </c>
       <c r="J354" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K354" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L354">
         <v>80133102</v>
@@ -17530,7 +17530,7 @@
         <v>247</v>
       </c>
       <c r="F355" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G355" t="s">
         <v>219</v>
@@ -17540,10 +17540,10 @@
         <v>86</v>
       </c>
       <c r="J355" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K355" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L355">
         <v>81133102</v>
@@ -17575,7 +17575,7 @@
         <v>247</v>
       </c>
       <c r="F356" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G356" t="s">
         <v>221</v>
@@ -17585,10 +17585,10 @@
         <v>86</v>
       </c>
       <c r="J356" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K356" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L356">
         <v>90133102</v>
@@ -17620,16 +17620,16 @@
         <v>247</v>
       </c>
       <c r="F357" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I357" t="s">
         <v>86</v>
       </c>
       <c r="J357" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K357" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L357">
         <v>90133102</v>
@@ -17661,7 +17661,7 @@
         <v>247</v>
       </c>
       <c r="F358" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G358" s="5" t="s">
         <v>220</v>
@@ -17670,10 +17670,10 @@
         <v>86</v>
       </c>
       <c r="J358" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K358" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L358">
         <v>80111101</v>
@@ -17705,7 +17705,7 @@
         <v>247</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G359" s="5" t="s">
         <v>221</v>
@@ -17714,10 +17714,10 @@
         <v>86</v>
       </c>
       <c r="J359" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K359" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L359">
         <v>81111101</v>
@@ -17749,16 +17749,16 @@
         <v>325</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I360" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J360" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K360" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L360">
         <v>80215106</v>
@@ -17791,10 +17791,10 @@
   <sheetData>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17802,15 +17802,15 @@
         <v>351</v>
       </c>
       <c r="B3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17818,15 +17818,15 @@
         <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17834,7 +17834,7 @@
         <v>323</v>
       </c>
       <c r="B7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17842,7 +17842,7 @@
         <v>290</v>
       </c>
       <c r="B8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17850,15 +17850,15 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B10" t="s">
         <v>444</v>
-      </c>
-      <c r="B10" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17866,7 +17866,7 @@
         <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17874,7 +17874,7 @@
         <v>300</v>
       </c>
       <c r="B12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.35">
@@ -17882,15 +17882,15 @@
         <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/backend/prisma/data/expense-line-items.xlsx
+++ b/backend/prisma/data/expense-line-items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22C5CD5-4330-4943-873D-82AB26DC2A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D336090E-2934-4E30-BA17-06665BAB9329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D30BD04-AED0-48C4-A0F0-DC51EF4C24C2}"/>
   </bookViews>
@@ -3889,10 +3889,8 @@
       <c r="F38" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
+      <c r="G38" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I38" t="s">
         <v>443</v>
@@ -3935,10 +3933,8 @@
       <c r="F39" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>OCLP</t>
-        </is>
+      <c r="G39" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I39" t="s">
         <v>443</v>
@@ -10849,10 +10845,8 @@
       <c r="F195" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
+      <c r="G195" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I195" t="s">
         <v>84</v>
@@ -10895,10 +10889,8 @@
       <c r="F196" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G196" s="5" t="inlineStr">
-        <is>
-          <t>OCLP</t>
-        </is>
+      <c r="G196" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I196" t="s">
         <v>84</v>
@@ -10941,10 +10933,8 @@
       <c r="F197" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G197" s="5" t="inlineStr">
-        <is>
-          <t>OLC</t>
-        </is>
+      <c r="G197" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="I197" t="s">
         <v>84</v>
@@ -11392,10 +11382,8 @@
       <c r="F207" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G207" s="5" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
+      <c r="G207" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="I207" t="s">
         <v>84</v>
@@ -11438,10 +11426,8 @@
       <c r="F208" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t>OCLP</t>
-        </is>
+      <c r="G208" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="I208" t="s">
         <v>84</v>
@@ -11484,10 +11470,8 @@
       <c r="F209" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G209" s="5" t="inlineStr">
-        <is>
-          <t>OLC</t>
-        </is>
+      <c r="G209" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="I209" t="s">
         <v>84</v>
@@ -16529,9 +16513,6 @@
       <c r="M329">
         <v>52111102</v>
       </c>
-      <c r="R329" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A330" t="str">
@@ -16570,9 +16551,6 @@
       <c r="M330">
         <v>52111102</v>
       </c>
-      <c r="R330" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A331" t="str">
@@ -16614,9 +16592,6 @@
       <c r="N331" t="s">
         <v>249</v>
       </c>
-      <c r="R331" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A332" t="str">
@@ -16655,9 +16630,6 @@
       <c r="M332">
         <v>52111101</v>
       </c>
-      <c r="R332" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A333" t="str">
@@ -16696,9 +16668,6 @@
       <c r="M333">
         <v>52061103</v>
       </c>
-      <c r="R333" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A334" t="str">
@@ -16737,9 +16706,6 @@
       <c r="M334">
         <v>52061101</v>
       </c>
-      <c r="R334" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A335" t="str">
@@ -16778,9 +16744,6 @@
       <c r="M335">
         <v>52061103</v>
       </c>
-      <c r="R335" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A336" t="str">
@@ -16818,9 +16781,6 @@
       </c>
       <c r="M336">
         <v>52061105</v>
-      </c>
-      <c r="R336" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.35">
